--- a/research/traditional_assets/database/data/sweden/sweden_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.011185</v>
+        <v>-0.0163</v>
       </c>
       <c r="E2">
-        <v>0.0431</v>
+        <v>0.0503</v>
       </c>
       <c r="G2">
-        <v>0.004006346025384101</v>
+        <v>0.002118388929638834</v>
       </c>
       <c r="H2">
-        <v>0.003623914495657982</v>
+        <v>1.824624401067082e-05</v>
       </c>
       <c r="I2">
-        <v>0.005527722110888443</v>
+        <v>-0.01205529341784994</v>
       </c>
       <c r="J2">
-        <v>0.004916928882340362</v>
+        <v>-0.0111950807650291</v>
       </c>
       <c r="K2">
-        <v>94.28</v>
+        <v>162.391</v>
       </c>
       <c r="L2">
-        <v>0.1574482297929191</v>
+        <v>0.2963025811136777</v>
       </c>
       <c r="M2">
-        <v>74.72</v>
+        <v>141.05544</v>
       </c>
       <c r="N2">
-        <v>0.06048733101270946</v>
+        <v>0.1243151604886045</v>
       </c>
       <c r="O2">
-        <v>0.7925328807806533</v>
+        <v>0.8686161178883067</v>
       </c>
       <c r="P2">
-        <v>72.78</v>
+        <v>139.49544</v>
       </c>
       <c r="Q2">
-        <v>0.05891686230065572</v>
+        <v>0.1229402992967056</v>
       </c>
       <c r="R2">
-        <v>0.7719558761137039</v>
+        <v>0.859009674181451</v>
       </c>
       <c r="S2">
-        <v>1.939999999999998</v>
+        <v>1.560000000000002</v>
       </c>
       <c r="T2">
-        <v>0.02596359743040682</v>
+        <v>0.01105948129331277</v>
       </c>
       <c r="U2">
-        <v>527.6</v>
+        <v>453.864</v>
       </c>
       <c r="V2">
-        <v>0.4271027280822473</v>
+        <v>0.4</v>
       </c>
       <c r="W2">
-        <v>0.05069434203409052</v>
+        <v>-0.09999999999999999</v>
       </c>
       <c r="X2">
-        <v>0.02800497930615125</v>
+        <v>0.05082464728384643</v>
       </c>
       <c r="Y2">
-        <v>0.02268936272793927</v>
+        <v>-0.1508246472838464</v>
       </c>
       <c r="Z2">
-        <v>0.2325255387831863</v>
+        <v>0.1962866355482604</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02443123871171364</v>
+        <v>0.04891956368755596</v>
       </c>
       <c r="AC2">
-        <v>-0.02443123871171364</v>
+        <v>-0.05017856486373645</v>
       </c>
       <c r="AD2">
-        <v>1738.562</v>
+        <v>1220.555</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1738.562</v>
+        <v>1220.555</v>
       </c>
       <c r="AG2">
-        <v>1210.962</v>
+        <v>766.691</v>
       </c>
       <c r="AH2">
-        <v>0.5846142154545166</v>
+        <v>0.5182350655884919</v>
       </c>
       <c r="AI2">
-        <v>0.5244970769796079</v>
+        <v>0.5011403971579372</v>
       </c>
       <c r="AJ2">
-        <v>0.4950254715153161</v>
+        <v>0.4032348577406276</v>
       </c>
       <c r="AK2">
-        <v>0.4344847480662848</v>
+        <v>0.3868872594163268</v>
       </c>
       <c r="AL2">
-        <v>0.02</v>
+        <v>0.196</v>
       </c>
       <c r="AM2">
-        <v>0.02</v>
+        <v>0.196</v>
       </c>
       <c r="AN2">
-        <v>514.3674556213018</v>
+        <v>-279.5590929912964</v>
       </c>
       <c r="AO2">
-        <v>165.5</v>
+        <v>-33.70918367346938</v>
       </c>
       <c r="AP2">
-        <v>358.2727810650888</v>
+        <v>-175.6049015116812</v>
       </c>
       <c r="AQ2">
-        <v>165.5</v>
+        <v>-33.70918367346938</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spotlight Group AB (publ) (NGM:SPGR)</t>
+          <t>XBT Provider AB (publ) (BST:0LNB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,116 +721,107 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.222</v>
+      </c>
+      <c r="E3">
+        <v>-0.546</v>
+      </c>
       <c r="G3">
-        <v>0.1028436018957346</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1028436018957346</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1568720379146919</v>
+        <v>0.03631284916201118</v>
       </c>
       <c r="J3">
-        <v>0.1225413791613247</v>
+        <v>0.02793296089385475</v>
       </c>
       <c r="K3">
-        <v>2.6</v>
+        <v>0.011</v>
       </c>
       <c r="L3">
-        <v>0.1232227488151659</v>
+        <v>0.03072625698324022</v>
       </c>
       <c r="M3">
-        <v>1.18</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01976549413735343</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.4538461538461538</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1.18</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01976549413735343</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.4538461538461538</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>7.239534151715455e-05</v>
       </c>
       <c r="W3">
-        <v>0.3452855245683931</v>
+        <v>0.02964959568733154</v>
       </c>
       <c r="X3">
-        <v>0.02298708535673973</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="Y3">
-        <v>0.3222984392116534</v>
+        <v>-0.01848525852413129</v>
       </c>
       <c r="Z3">
-        <v>4.064727412829898</v>
+        <v>1.056047197640118</v>
       </c>
       <c r="AA3">
-        <v>0.4980973030830189</v>
+        <v>0.02949852507374631</v>
       </c>
       <c r="AB3">
-        <v>0.02299964385269673</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="AC3">
-        <v>0.4750976592303222</v>
+        <v>-0.01863632913771652</v>
       </c>
       <c r="AD3">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.462</v>
+        <v>-0.023</v>
       </c>
       <c r="AH3">
-        <v>0.007679265981849007</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.04609858311714229</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.007679265981849007</v>
+        <v>-7.240058298208558e-05</v>
       </c>
       <c r="AK3">
-        <v>0.04609858311714229</v>
+        <v>-0.07744107744107745</v>
       </c>
       <c r="AL3">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.02</v>
-      </c>
-      <c r="AN3">
-        <v>0.1366863905325444</v>
-      </c>
-      <c r="AO3">
-        <v>165.5</v>
-      </c>
-      <c r="AP3">
-        <v>0.1366863905325444</v>
-      </c>
-      <c r="AQ3">
-        <v>165.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Resurs Holding AB (publ) (OM:RESURS)</t>
+          <t>Qliro AB (publ) (OM:QLIRO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,12 +840,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0193</v>
-      </c>
-      <c r="E4">
-        <v>0.0431</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -868,85 +853,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>112.9</v>
+        <v>-6.44</v>
       </c>
       <c r="L4">
-        <v>0.3832315003394433</v>
+        <v>-0.23</v>
       </c>
       <c r="M4">
-        <v>63.23999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07523197715917201</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.5601417183348095</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>61.3</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.07292410183202473</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.5429583702391496</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.939999999999998</v>
-      </c>
-      <c r="T4">
-        <v>0.03067678684376973</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>495.2</v>
+        <v>49.6</v>
       </c>
       <c r="V4">
-        <v>0.5891030216512015</v>
+        <v>2</v>
       </c>
       <c r="W4">
-        <v>0.1300241851894507</v>
+        <v>-0.09999999999999999</v>
       </c>
       <c r="X4">
-        <v>0.02932591641366036</v>
+        <v>0.05082464728384643</v>
       </c>
       <c r="Y4">
-        <v>0.1006982687757903</v>
+        <v>-0.1508246472838464</v>
       </c>
       <c r="Z4">
-        <v>0.2498727735368957</v>
+        <v>0.4658901830282862</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02386168426822117</v>
+        <v>0.04891956368755596</v>
       </c>
       <c r="AC4">
-        <v>-0.02386168426822117</v>
+        <v>-0.04891956368755596</v>
       </c>
       <c r="AD4">
-        <v>862.6</v>
+        <v>9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>862.6</v>
+        <v>9</v>
       </c>
       <c r="AG4">
-        <v>367.4</v>
+        <v>-40.6</v>
       </c>
       <c r="AH4">
-        <v>0.5064584311883513</v>
+        <v>0.2662721893491125</v>
       </c>
       <c r="AI4">
-        <v>0.477154552494745</v>
+        <v>0.1672862453531599</v>
       </c>
       <c r="AJ4">
-        <v>0.3041390728476822</v>
+        <v>2.569620253164557</v>
       </c>
       <c r="AK4">
-        <v>0.2799024836202956</v>
+        <v>-9.666666666666677</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qliro AB (publ) (OM:QLIRO)</t>
+          <t>Resurs Holding AB (publ) (OM:RESURS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -971,6 +953,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.0163</v>
+      </c>
+      <c r="E5">
+        <v>0.0503</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -984,82 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-4.62</v>
+        <v>119.1</v>
       </c>
       <c r="L5">
-        <v>-0.1294117647058823</v>
+        <v>0.556282111163008</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>131.46</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.2746187591393357</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.103778337531486</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>129.9</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.2713599331522875</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.090680100755668</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.560000000000002</v>
+      </c>
+      <c r="T5">
+        <v>0.01186672752167961</v>
       </c>
       <c r="U5">
-        <v>32.4</v>
+        <v>392.6</v>
       </c>
       <c r="V5">
-        <v>0.6937901498929335</v>
+        <v>0.8201378734071444</v>
       </c>
       <c r="W5">
-        <v>-0.06885245901639345</v>
+        <v>0.1260050782903089</v>
       </c>
       <c r="X5">
-        <v>0.02668404219864214</v>
+        <v>0.05774381421932843</v>
       </c>
       <c r="Y5">
-        <v>-0.09553650121503558</v>
+        <v>0.06826126407098047</v>
       </c>
       <c r="Z5">
-        <v>0.4165208260413021</v>
+        <v>0.1631113819899436</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02500079315520611</v>
+        <v>0.04979856805857593</v>
       </c>
       <c r="AC5">
-        <v>-0.02500079315520611</v>
+        <v>-0.04979856805857593</v>
       </c>
       <c r="AD5">
-        <v>28.1</v>
+        <v>620.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>28.1</v>
+        <v>620.6</v>
       </c>
       <c r="AG5">
-        <v>-4.299999999999997</v>
+        <v>228</v>
       </c>
       <c r="AH5">
-        <v>0.3756684491978609</v>
+        <v>0.5645410715910125</v>
       </c>
       <c r="AI5">
-        <v>0.3037837837837838</v>
+        <v>0.4775682954982686</v>
       </c>
       <c r="AJ5">
-        <v>-0.1014150943396226</v>
+        <v>0.3226262912126786</v>
       </c>
       <c r="AK5">
-        <v>-0.07154742096505817</v>
+        <v>0.2514058881905392</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,10 +1076,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00307</v>
+        <v>0.0452</v>
+      </c>
+      <c r="E6">
+        <v>0.0512</v>
       </c>
       <c r="G6">
-        <v>0.000925626515763945</v>
+        <v>0.0003398791540785498</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1100,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-16.6</v>
+        <v>56.2</v>
       </c>
       <c r="L6">
-        <v>-0.06709781729991916</v>
+        <v>0.2122356495468278</v>
       </c>
       <c r="M6">
-        <v>10.3</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N6">
-        <v>0.03572667360388485</v>
+        <v>0.0338479809976247</v>
       </c>
       <c r="O6">
-        <v>-0.6204819277108433</v>
+        <v>0.152135231316726</v>
       </c>
       <c r="P6">
-        <v>10.3</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q6">
-        <v>0.03572667360388485</v>
+        <v>0.0338479809976247</v>
       </c>
       <c r="R6">
-        <v>-0.6204819277108433</v>
+        <v>0.152135231316726</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1136,55 +1130,418 @@
         <v>0</v>
       </c>
       <c r="W6">
-        <v>-0.02863550112126962</v>
+        <v>0.1008976660682226</v>
       </c>
       <c r="X6">
-        <v>0.04123341679052178</v>
+        <v>0.06490399962076489</v>
       </c>
       <c r="Y6">
-        <v>-0.06986891791179141</v>
+        <v>0.03599366644745775</v>
       </c>
       <c r="Z6">
-        <v>0.189534972803187</v>
+        <v>0.1885502705781829</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.02703418648130906</v>
+        <v>0.05017856486373645</v>
       </c>
       <c r="AC6">
-        <v>-0.02703418648130906</v>
+        <v>-0.05017856486373645</v>
       </c>
       <c r="AD6">
-        <v>847.4</v>
+        <v>571.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>847.4</v>
+        <v>571.5</v>
       </c>
       <c r="AG6">
-        <v>847.4</v>
+        <v>571.5</v>
       </c>
       <c r="AH6">
-        <v>0.7461477502861671</v>
+        <v>0.6934838005096469</v>
       </c>
       <c r="AI6">
-        <v>0.6033893477641697</v>
+        <v>0.5464193517544698</v>
       </c>
       <c r="AJ6">
-        <v>0.7461477502861671</v>
+        <v>0.6934838005096469</v>
       </c>
       <c r="AK6">
-        <v>0.6033893477641697</v>
+        <v>0.5464193517544698</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spotlight Group AB (publ) (NGM:SPGR)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0.2700680272108844</v>
+      </c>
+      <c r="H7">
+        <v>0.2700680272108844</v>
+      </c>
+      <c r="I7">
+        <v>-0.1340136054421769</v>
+      </c>
+      <c r="J7">
+        <v>-0.1340136054421769</v>
+      </c>
+      <c r="K7">
+        <v>-1.75</v>
+      </c>
+      <c r="L7">
+        <v>-0.1190476190476191</v>
+      </c>
+      <c r="M7">
+        <v>1.04544</v>
+      </c>
+      <c r="N7">
+        <v>0.07260000000000001</v>
+      </c>
+      <c r="O7">
+        <v>-0.5973942857142858</v>
+      </c>
+      <c r="P7">
+        <v>1.04544</v>
+      </c>
+      <c r="Q7">
+        <v>0.07260000000000001</v>
+      </c>
+      <c r="R7">
+        <v>-0.5973942857142858</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>-0.1826722338204593</v>
+      </c>
+      <c r="X7">
+        <v>0.04847199154686252</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2311442253673218</v>
+      </c>
+      <c r="Z7">
+        <v>2.401176086246325</v>
+      </c>
+      <c r="AA7">
+        <v>-0.3217902646194054</v>
+      </c>
+      <c r="AB7">
+        <v>0.04839434037029693</v>
+      </c>
+      <c r="AC7">
+        <v>-0.3701846049897023</v>
+      </c>
+      <c r="AD7">
+        <v>0.655</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0.655</v>
+      </c>
+      <c r="AG7">
+        <v>0.655</v>
+      </c>
+      <c r="AH7">
+        <v>0.04350714048488875</v>
+      </c>
+      <c r="AI7">
+        <v>0.09857035364936041</v>
+      </c>
+      <c r="AJ7">
+        <v>0.04350714048488875</v>
+      </c>
+      <c r="AK7">
+        <v>0.09857035364936041</v>
+      </c>
+      <c r="AL7">
+        <v>0.044</v>
+      </c>
+      <c r="AM7">
+        <v>0.044</v>
+      </c>
+      <c r="AN7">
+        <v>-0.4962121212121212</v>
+      </c>
+      <c r="AO7">
+        <v>-44.77272727272727</v>
+      </c>
+      <c r="AP7">
+        <v>-0.4962121212121212</v>
+      </c>
+      <c r="AQ7">
+        <v>-44.77272727272727</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SaveLend Group AB (publ) (OM:YIELD)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>-0.1995934959349593</v>
+      </c>
+      <c r="H8">
+        <v>-0.2357723577235772</v>
+      </c>
+      <c r="I8">
+        <v>-0.2447154471544715</v>
+      </c>
+      <c r="J8">
+        <v>-0.2447154471544715</v>
+      </c>
+      <c r="K8">
+        <v>-3.07</v>
+      </c>
+      <c r="L8">
+        <v>-0.2495934959349593</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>10.7</v>
+      </c>
+      <c r="V8">
+        <v>0.2517647058823529</v>
+      </c>
+      <c r="W8">
+        <v>-0.375764993880049</v>
+      </c>
+      <c r="X8">
+        <v>0.05141351858288278</v>
+      </c>
+      <c r="Y8">
+        <v>-0.4271785124629318</v>
+      </c>
+      <c r="Z8">
+        <v>1.435239206534422</v>
+      </c>
+      <c r="AA8">
+        <v>-0.3512252042007001</v>
+      </c>
+      <c r="AB8">
+        <v>0.04903867112190079</v>
+      </c>
+      <c r="AC8">
+        <v>-0.4002638753226009</v>
+      </c>
+      <c r="AD8">
+        <v>18.8</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>18.8</v>
+      </c>
+      <c r="AG8">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="AH8">
+        <v>0.3066884176182708</v>
+      </c>
+      <c r="AI8">
+        <v>0.6950092421441775</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1600790513833992</v>
+      </c>
+      <c r="AK8">
+        <v>0.4954128440366973</v>
+      </c>
+      <c r="AL8">
+        <v>0.134</v>
+      </c>
+      <c r="AM8">
+        <v>0.134</v>
+      </c>
+      <c r="AN8">
+        <v>-9.126213592233009</v>
+      </c>
+      <c r="AO8">
+        <v>-22.46268656716418</v>
+      </c>
+      <c r="AP8">
+        <v>-3.932038834951457</v>
+      </c>
+      <c r="AQ8">
+        <v>-22.46268656716418</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Goobit Group AB (publ) (OM:BTCX)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>-0.03217391304347826</v>
+      </c>
+      <c r="H9">
+        <v>-0.07681159420289856</v>
+      </c>
+      <c r="I9">
+        <v>-0.1188405797101449</v>
+      </c>
+      <c r="J9">
+        <v>-0.1188405797101449</v>
+      </c>
+      <c r="K9">
+        <v>-1.66</v>
+      </c>
+      <c r="L9">
+        <v>-0.1202898550724638</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="V9">
+        <v>0.2376262626262626</v>
+      </c>
+      <c r="X9">
+        <v>0.04813485421146283</v>
+      </c>
+      <c r="AB9">
+        <v>0.04813485421146283</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>-0.9409999999999999</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.3116926134481616</v>
+      </c>
+      <c r="AK9">
+        <v>-0.6726233023588277</v>
+      </c>
+      <c r="AL9">
+        <v>0.018</v>
+      </c>
+      <c r="AM9">
+        <v>0.018</v>
+      </c>
+      <c r="AN9">
+        <v>-0</v>
+      </c>
+      <c r="AO9">
+        <v>-91.11111111111111</v>
+      </c>
+      <c r="AP9">
+        <v>0.9543610547667343</v>
+      </c>
+      <c r="AQ9">
+        <v>-91.11111111111111</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0163</v>
+        <v>0.04535</v>
       </c>
       <c r="E2">
-        <v>0.0503</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="G2">
-        <v>0.002118388929638834</v>
+        <v>-0.003953074433656958</v>
       </c>
       <c r="H2">
-        <v>1.824624401067082e-05</v>
+        <v>-0.007932038834951456</v>
       </c>
       <c r="I2">
-        <v>-0.01205529341784994</v>
+        <v>-0.006406148867313916</v>
       </c>
       <c r="J2">
-        <v>-0.0111950807650291</v>
+        <v>-0.006117951057248524</v>
       </c>
       <c r="K2">
-        <v>162.391</v>
+        <v>133.14</v>
       </c>
       <c r="L2">
-        <v>0.2963025811136777</v>
+        <v>0.2154368932038835</v>
       </c>
       <c r="M2">
-        <v>141.05544</v>
+        <v>49.4558</v>
       </c>
       <c r="N2">
-        <v>0.1243151604886045</v>
+        <v>0.05369677097131442</v>
       </c>
       <c r="O2">
-        <v>0.8686161178883067</v>
+        <v>0.3714571128135797</v>
       </c>
       <c r="P2">
-        <v>139.49544</v>
+        <v>48.8348</v>
       </c>
       <c r="Q2">
-        <v>0.1229402992967056</v>
+        <v>0.05302251851208443</v>
       </c>
       <c r="R2">
-        <v>0.859009674181451</v>
+        <v>0.3667928496319663</v>
       </c>
       <c r="S2">
-        <v>1.560000000000002</v>
+        <v>0.6210000000000022</v>
       </c>
       <c r="T2">
-        <v>0.01105948129331277</v>
+        <v>0.01255666676102706</v>
       </c>
       <c r="U2">
-        <v>453.864</v>
+        <v>403.818</v>
       </c>
       <c r="V2">
-        <v>0.4</v>
+        <v>0.4384465049618901</v>
       </c>
       <c r="W2">
-        <v>-0.09999999999999999</v>
+        <v>-0.1018181818181818</v>
       </c>
       <c r="X2">
-        <v>0.05082464728384643</v>
+        <v>0.05187956004724464</v>
       </c>
       <c r="Y2">
-        <v>-0.1508246472838464</v>
+        <v>-0.1536977418654265</v>
       </c>
       <c r="Z2">
-        <v>0.1962866355482604</v>
+        <v>0.3072178293718141</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>-0.04900849858356941</v>
       </c>
       <c r="AB2">
-        <v>0.04891956368755596</v>
+        <v>0.04968538029098273</v>
       </c>
       <c r="AC2">
-        <v>-0.05017856486373645</v>
+        <v>-0.097080301782099</v>
       </c>
       <c r="AD2">
-        <v>1220.555</v>
+        <v>1075.951</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1220.555</v>
+        <v>1075.951</v>
       </c>
       <c r="AG2">
-        <v>766.691</v>
+        <v>672.133</v>
       </c>
       <c r="AH2">
-        <v>0.5182350655884919</v>
+        <v>0.5387914997263356</v>
       </c>
       <c r="AI2">
-        <v>0.5011403971579372</v>
+        <v>0.4423973270747982</v>
       </c>
       <c r="AJ2">
-        <v>0.4032348577406276</v>
+        <v>0.4218885442892177</v>
       </c>
       <c r="AK2">
-        <v>0.3868872594163268</v>
+        <v>0.3313817561138189</v>
       </c>
       <c r="AL2">
-        <v>0.196</v>
+        <v>3.056</v>
       </c>
       <c r="AM2">
-        <v>0.196</v>
+        <v>1.785</v>
       </c>
       <c r="AN2">
-        <v>-279.5590929912964</v>
+        <v>-537975.4999999696</v>
       </c>
       <c r="AO2">
-        <v>-33.70918367346938</v>
+        <v>-1.295484293193717</v>
       </c>
       <c r="AP2">
-        <v>-175.6049015116812</v>
+        <v>-336066.4999999811</v>
       </c>
       <c r="AQ2">
-        <v>-33.70918367346938</v>
+        <v>-2.217927170868347</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XBT Provider AB (publ) (BST:0LNB)</t>
+          <t>ScandBook Holding AB (publ) (OM:SBOK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,106 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.222</v>
+        <v>0.0594</v>
       </c>
       <c r="E3">
-        <v>-0.546</v>
+        <v>0.426</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1455056179775281</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1455056179775281</v>
       </c>
       <c r="I3">
-        <v>0.03631284916201118</v>
+        <v>0.07050561797752808</v>
       </c>
       <c r="J3">
-        <v>0.02793296089385475</v>
+        <v>0.06488264927105579</v>
       </c>
       <c r="K3">
-        <v>0.011</v>
+        <v>2.23</v>
       </c>
       <c r="L3">
-        <v>0.03072625698324022</v>
+        <v>0.06264044943820224</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.6348</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05334453781512605</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2846636771300449</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.6348</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05334453781512605</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2846636771300449</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.023</v>
+        <v>3.86</v>
       </c>
       <c r="V3">
-        <v>7.239534151715455e-05</v>
+        <v>0.3243697478991596</v>
       </c>
       <c r="W3">
-        <v>0.02964959568733154</v>
+        <v>0.1061904761904762</v>
       </c>
       <c r="X3">
-        <v>0.04813485421146283</v>
+        <v>0.0516916389520337</v>
       </c>
       <c r="Y3">
-        <v>-0.01848525852413129</v>
+        <v>0.0544988372384425</v>
       </c>
       <c r="Z3">
-        <v>1.056047197640118</v>
+        <v>2.04245553643144</v>
       </c>
       <c r="AA3">
-        <v>0.02949852507374631</v>
+        <v>0.1325199262220073</v>
       </c>
       <c r="AB3">
-        <v>0.04813485421146283</v>
+        <v>0.04888090419579245</v>
       </c>
       <c r="AC3">
-        <v>-0.01863632913771652</v>
+        <v>0.0836390220262148</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG3">
-        <v>-0.023</v>
+        <v>-1.31</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.09826589595375722</v>
       </c>
       <c r="AJ3">
-        <v>-7.240058298208558e-05</v>
+        <v>-0.1237016052880076</v>
       </c>
       <c r="AK3">
-        <v>-0.07744107744107745</v>
+        <v>-0.05930285196921684</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.117</v>
+      </c>
+      <c r="AN3">
+        <v>0.6234718826405867</v>
+      </c>
+      <c r="AO3">
+        <v>19.609375</v>
+      </c>
+      <c r="AP3">
+        <v>-0.3202933985330074</v>
+      </c>
+      <c r="AQ3">
+        <v>21.45299145299145</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qliro AB (publ) (OM:QLIRO)</t>
+          <t>Hoist Finance AB (publ) (OM:HOFI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,8 +855,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0313</v>
+      </c>
+      <c r="E4">
+        <v>0.08810000000000001</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.0006393328700486448</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -853,82 +874,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-6.44</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L4">
-        <v>-0.23</v>
+        <v>0.2480889506601807</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>11.7</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.03557312252964427</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.1638655462184874</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>11.7</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.03557312252964427</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.1638655462184874</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>49.6</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>-0.09999999999999999</v>
+        <v>0.1505059021922429</v>
       </c>
       <c r="X4">
-        <v>0.05082464728384643</v>
+        <v>0.06295852229010111</v>
       </c>
       <c r="Y4">
-        <v>-0.1508246472838464</v>
+        <v>0.08754737990214174</v>
       </c>
       <c r="Z4">
-        <v>0.4658901830282862</v>
+        <v>0.2751697102973515</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04891956368755596</v>
+        <v>0.04940250018009022</v>
       </c>
       <c r="AC4">
-        <v>-0.04891956368755596</v>
+        <v>-0.04940250018009022</v>
       </c>
       <c r="AD4">
-        <v>9</v>
+        <v>494.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>494.1</v>
       </c>
       <c r="AG4">
-        <v>-40.6</v>
+        <v>494.1</v>
       </c>
       <c r="AH4">
-        <v>0.2662721893491125</v>
+        <v>0.6003645200486027</v>
       </c>
       <c r="AI4">
-        <v>0.1672862453531599</v>
+        <v>0.475736568457539</v>
       </c>
       <c r="AJ4">
-        <v>2.569620253164557</v>
+        <v>0.6003645200486027</v>
       </c>
       <c r="AK4">
-        <v>-9.666666666666677</v>
+        <v>0.475736568457539</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,10 +978,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0163</v>
+        <v>-0.0344</v>
       </c>
       <c r="E5">
-        <v>0.0503</v>
+        <v>-0.07730000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,85 +996,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>119.1</v>
+        <v>70.5</v>
       </c>
       <c r="L5">
-        <v>0.556282111163008</v>
+        <v>0.3207461328480437</v>
       </c>
       <c r="M5">
-        <v>131.46</v>
+        <v>37.121</v>
       </c>
       <c r="N5">
-        <v>0.2746187591393357</v>
+        <v>0.07839704329461458</v>
       </c>
       <c r="O5">
-        <v>1.103778337531486</v>
+        <v>0.5265390070921986</v>
       </c>
       <c r="P5">
-        <v>129.9</v>
+        <v>36.5</v>
       </c>
       <c r="Q5">
-        <v>0.2713599331522875</v>
+        <v>0.07708553326293559</v>
       </c>
       <c r="R5">
-        <v>1.090680100755668</v>
+        <v>0.5177304964539007</v>
       </c>
       <c r="S5">
-        <v>1.560000000000002</v>
+        <v>0.6210000000000022</v>
       </c>
       <c r="T5">
-        <v>0.01186672752167961</v>
+        <v>0.01672907518655214</v>
       </c>
       <c r="U5">
-        <v>392.6</v>
+        <v>371.2</v>
       </c>
       <c r="V5">
-        <v>0.8201378734071444</v>
+        <v>0.7839493136219641</v>
       </c>
       <c r="W5">
-        <v>0.1260050782903089</v>
+        <v>0.103844454264251</v>
       </c>
       <c r="X5">
-        <v>0.05774381421932843</v>
+        <v>0.05976005854245253</v>
       </c>
       <c r="Y5">
-        <v>0.06826126407098047</v>
+        <v>0.04408439572179847</v>
       </c>
       <c r="Z5">
-        <v>0.1631113819899436</v>
+        <v>0.2423640974749146</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04979856805857593</v>
+        <v>0.04944973366991329</v>
       </c>
       <c r="AC5">
-        <v>-0.04979856805857593</v>
+        <v>-0.04944973366991329</v>
       </c>
       <c r="AD5">
-        <v>620.6</v>
+        <v>538.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>620.6</v>
+        <v>538.2</v>
       </c>
       <c r="AG5">
-        <v>228</v>
+        <v>167.0000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.5645410715910125</v>
+        <v>0.5319758821785114</v>
       </c>
       <c r="AI5">
-        <v>0.4775682954982686</v>
+        <v>0.4272445820433437</v>
       </c>
       <c r="AJ5">
-        <v>0.3226262912126786</v>
+        <v>0.2607338017174083</v>
       </c>
       <c r="AK5">
-        <v>0.2514058881905392</v>
+        <v>0.1879572312886889</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hoist Finance AB (publ) (OM:HOFI)</t>
+          <t>Qliro AB (publ) (OM:QLIRO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1100,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0452</v>
-      </c>
-      <c r="E6">
-        <v>0.0512</v>
+        <v>0.0688</v>
       </c>
       <c r="G6">
-        <v>0.0003398791540785498</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1094,85 +1115,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>56.2</v>
+        <v>-3.17</v>
       </c>
       <c r="L6">
-        <v>0.2122356495468278</v>
+        <v>-0.1081911262798635</v>
       </c>
       <c r="M6">
-        <v>8.550000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.0338479809976247</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.152135231316726</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>8.550000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.0338479809976247</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.152135231316726</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>0.579345088161209</v>
       </c>
       <c r="W6">
-        <v>0.1008976660682226</v>
+        <v>-0.07075892857142857</v>
       </c>
       <c r="X6">
-        <v>0.06490399962076489</v>
+        <v>0.05187956004724464</v>
       </c>
       <c r="Y6">
-        <v>0.03599366644745775</v>
+        <v>-0.1226384886186732</v>
       </c>
       <c r="Z6">
-        <v>0.1885502705781829</v>
+        <v>6.976190476190483</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05017856486373645</v>
+        <v>0.04968538029098273</v>
       </c>
       <c r="AC6">
-        <v>-0.05017856486373645</v>
+        <v>-0.04968538029098273</v>
       </c>
       <c r="AD6">
-        <v>571.5</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>571.5</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AG6">
-        <v>571.5</v>
+        <v>-13.64</v>
       </c>
       <c r="AH6">
-        <v>0.6934838005096469</v>
+        <v>0.1907867916836526</v>
       </c>
       <c r="AI6">
-        <v>0.5464193517544698</v>
+        <v>0.1767371601208459</v>
       </c>
       <c r="AJ6">
-        <v>0.6934838005096469</v>
+        <v>-0.523407521105142</v>
       </c>
       <c r="AK6">
-        <v>0.5464193517544698</v>
+        <v>-0.4552736982643525</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spotlight Group AB (publ) (NGM:SPGR)</t>
+          <t>SaveLend Group AB (publ) (OM:YIELD)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,115 +1216,112 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.2700680272108844</v>
+        <v>-0.04925465838509317</v>
       </c>
       <c r="H7">
-        <v>0.2700680272108844</v>
+        <v>-0.108695652173913</v>
       </c>
       <c r="I7">
-        <v>-0.1340136054421769</v>
+        <v>-0.0322360248447205</v>
       </c>
       <c r="J7">
-        <v>-0.1340136054421769</v>
+        <v>-0.0322360248447205</v>
       </c>
       <c r="K7">
-        <v>-1.75</v>
+        <v>-0.84</v>
       </c>
       <c r="L7">
-        <v>-0.1190476190476191</v>
+        <v>-0.05217391304347825</v>
       </c>
       <c r="M7">
-        <v>1.04544</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.07260000000000001</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0.5973942857142858</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>1.04544</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.07260000000000001</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0.5973942857142858</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>0.0698051948051948</v>
       </c>
       <c r="W7">
-        <v>-0.1826722338204593</v>
+        <v>-0.1018181818181818</v>
       </c>
       <c r="X7">
-        <v>0.04847199154686252</v>
+        <v>0.0541057539809256</v>
       </c>
       <c r="Y7">
-        <v>-0.2311442253673218</v>
+        <v>-0.1559239357991074</v>
       </c>
       <c r="Z7">
-        <v>2.401176086246325</v>
+        <v>1.520302171860246</v>
       </c>
       <c r="AA7">
-        <v>-0.3217902646194054</v>
+        <v>-0.04900849858356941</v>
       </c>
       <c r="AB7">
-        <v>0.04839434037029693</v>
+        <v>0.04807180319852959</v>
       </c>
       <c r="AC7">
-        <v>-0.3701846049897023</v>
+        <v>-0.097080301782099</v>
       </c>
       <c r="AD7">
-        <v>0.655</v>
+        <v>15.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.655</v>
+        <v>15.1</v>
       </c>
       <c r="AG7">
-        <v>0.655</v>
+        <v>12.95</v>
       </c>
       <c r="AH7">
-        <v>0.04350714048488875</v>
+        <v>0.3289760348583878</v>
       </c>
       <c r="AI7">
-        <v>0.09857035364936041</v>
+        <v>0.6257770410277663</v>
       </c>
       <c r="AJ7">
-        <v>0.04350714048488875</v>
+        <v>0.296</v>
       </c>
       <c r="AK7">
-        <v>0.09857035364936041</v>
+        <v>0.5891719745222931</v>
       </c>
       <c r="AL7">
-        <v>0.044</v>
+        <v>0.177</v>
       </c>
       <c r="AM7">
-        <v>0.044</v>
+        <v>0.177</v>
       </c>
       <c r="AN7">
-        <v>-0.4962121212121212</v>
+        <v>58.75486381322957</v>
       </c>
       <c r="AO7">
-        <v>-44.77272727272727</v>
+        <v>-2.932203389830509</v>
       </c>
       <c r="AP7">
-        <v>-0.4962121212121212</v>
+        <v>50.38910505836576</v>
       </c>
       <c r="AQ7">
-        <v>-44.77272727272727</v>
+        <v>-2.932203389830509</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SaveLend Group AB (publ) (OM:YIELD)</t>
+          <t>Tessin Nordic Holding AB (publ) (OM:TESSIN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,22 +1341,22 @@
         </is>
       </c>
       <c r="G8">
-        <v>-0.1995934959349593</v>
+        <v>-0.6162946428571429</v>
       </c>
       <c r="H8">
-        <v>-0.2357723577235772</v>
+        <v>-0.7522321428571428</v>
       </c>
       <c r="I8">
-        <v>-0.2447154471544715</v>
+        <v>-0.4374999999999999</v>
       </c>
       <c r="J8">
-        <v>-0.2447154471544715</v>
+        <v>-0.4374999999999999</v>
       </c>
       <c r="K8">
-        <v>-3.07</v>
+        <v>-2.54</v>
       </c>
       <c r="L8">
-        <v>-0.2495934959349593</v>
+        <v>-0.5669642857142857</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1365,73 +1380,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>10.7</v>
+        <v>0.234</v>
       </c>
       <c r="V8">
-        <v>0.2517647058823529</v>
+        <v>0.08041237113402062</v>
       </c>
       <c r="W8">
-        <v>-0.375764993880049</v>
+        <v>-1.938931297709924</v>
       </c>
       <c r="X8">
-        <v>0.05141351858288278</v>
+        <v>0.09791401182419979</v>
       </c>
       <c r="Y8">
-        <v>-0.4271785124629318</v>
+        <v>-2.036845309534123</v>
       </c>
       <c r="Z8">
-        <v>1.435239206534422</v>
+        <v>0.2888086642599278</v>
       </c>
       <c r="AA8">
-        <v>-0.3512252042007001</v>
+        <v>-0.1263537906137184</v>
       </c>
       <c r="AB8">
-        <v>0.04903867112190079</v>
+        <v>0.05102584190419997</v>
       </c>
       <c r="AC8">
-        <v>-0.4002638753226009</v>
+        <v>-0.1773796325179184</v>
       </c>
       <c r="AD8">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="AG8">
-        <v>8.100000000000001</v>
+        <v>15.766</v>
       </c>
       <c r="AH8">
-        <v>0.3066884176182708</v>
+        <v>0.8461131676361713</v>
       </c>
       <c r="AI8">
-        <v>0.6950092421441775</v>
+        <v>0.8786381109280614</v>
       </c>
       <c r="AJ8">
-        <v>0.1600790513833992</v>
+        <v>0.8441850503319768</v>
       </c>
       <c r="AK8">
-        <v>0.4954128440366973</v>
+        <v>0.8770582999554962</v>
       </c>
       <c r="AL8">
-        <v>0.134</v>
+        <v>1.65</v>
       </c>
       <c r="AM8">
-        <v>0.134</v>
+        <v>0.3899999999999999</v>
       </c>
       <c r="AN8">
-        <v>-9.126213592233009</v>
+        <v>-8.37696335078534</v>
       </c>
       <c r="AO8">
-        <v>-22.46268656716418</v>
+        <v>-1.187878787878788</v>
       </c>
       <c r="AP8">
-        <v>-3.932038834951457</v>
+        <v>-8.254450261780105</v>
       </c>
       <c r="AQ8">
-        <v>-22.46268656716418</v>
+        <v>-5.025641025641026</v>
       </c>
     </row>
     <row r="9">
@@ -1442,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Goobit Group AB (publ) (OM:BTCX)</t>
+          <t>Rolling Optics Holding AB (publ) (OM:RO)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1451,22 +1466,22 @@
         </is>
       </c>
       <c r="G9">
-        <v>-0.03217391304347826</v>
+        <v>-0.5806167400881057</v>
       </c>
       <c r="H9">
-        <v>-0.07681159420289856</v>
+        <v>-0.6035242290748899</v>
       </c>
       <c r="I9">
-        <v>-0.1188405797101449</v>
+        <v>-0.5418502202643172</v>
       </c>
       <c r="J9">
-        <v>-0.1188405797101449</v>
+        <v>-0.5418502202643172</v>
       </c>
       <c r="K9">
-        <v>-1.66</v>
+        <v>-1.33</v>
       </c>
       <c r="L9">
-        <v>-0.1202898550724638</v>
+        <v>-0.5859030837004405</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1490,16 +1505,31 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.9409999999999999</v>
+        <v>2.97</v>
       </c>
       <c r="V9">
-        <v>0.2376262626262626</v>
+        <v>0.1993288590604027</v>
+      </c>
+      <c r="W9">
+        <v>-0.144880174291939</v>
       </c>
       <c r="X9">
-        <v>0.04813485421146283</v>
+        <v>0.04981714963548235</v>
+      </c>
+      <c r="Y9">
+        <v>-0.1946973239274213</v>
+      </c>
+      <c r="Z9">
+        <v>0.3767009624958514</v>
+      </c>
+      <c r="AA9">
+        <v>-0.2041154995021573</v>
       </c>
       <c r="AB9">
-        <v>0.04813485421146283</v>
+        <v>0.04981714963548235</v>
+      </c>
+      <c r="AC9">
+        <v>-0.2539326491376397</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1511,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-0.9409999999999999</v>
+        <v>-2.97</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1520,28 +1550,278 @@
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.3116926134481616</v>
+        <v>-0.2489522212908634</v>
       </c>
       <c r="AK9">
-        <v>-0.6726233023588277</v>
+        <v>-1.614130434782609</v>
       </c>
       <c r="AL9">
-        <v>0.018</v>
+        <v>0.255</v>
       </c>
       <c r="AM9">
-        <v>0.018</v>
+        <v>0.255</v>
       </c>
       <c r="AN9">
         <v>-0</v>
       </c>
       <c r="AO9">
-        <v>-91.11111111111111</v>
+        <v>-4.823529411764706</v>
       </c>
       <c r="AP9">
-        <v>0.9543610547667343</v>
+        <v>2.828571428571429</v>
       </c>
       <c r="AQ9">
-        <v>-91.11111111111111</v>
+        <v>-4.823529411764706</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Spotlight Group AB (publ) (NGM:SPGR)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>-0.1944055944055944</v>
+      </c>
+      <c r="H10">
+        <v>-0.1944055944055944</v>
+      </c>
+      <c r="I10">
+        <v>-0.1104895104895105</v>
+      </c>
+      <c r="J10">
+        <v>-0.1104895104895105</v>
+      </c>
+      <c r="K10">
+        <v>-1.4</v>
+      </c>
+      <c r="L10">
+        <v>-0.09790209790209789</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>-0.2306425041186161</v>
+      </c>
+      <c r="X10">
+        <v>0.05016115100821715</v>
+      </c>
+      <c r="Y10">
+        <v>-0.2808036551268333</v>
+      </c>
+      <c r="Z10">
+        <v>3.92318244170096</v>
+      </c>
+      <c r="AA10">
+        <v>-0.4334705075445816</v>
+      </c>
+      <c r="AB10">
+        <v>0.04979101688825568</v>
+      </c>
+      <c r="AC10">
+        <v>-0.4832615244328373</v>
+      </c>
+      <c r="AD10">
+        <v>0.641</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0.641</v>
+      </c>
+      <c r="AG10">
+        <v>0.641</v>
+      </c>
+      <c r="AH10">
+        <v>0.03783719969305235</v>
+      </c>
+      <c r="AI10">
+        <v>0.09129753596353796</v>
+      </c>
+      <c r="AJ10">
+        <v>0.03783719969305235</v>
+      </c>
+      <c r="AK10">
+        <v>0.09129753596353796</v>
+      </c>
+      <c r="AL10">
+        <v>0.309</v>
+      </c>
+      <c r="AM10">
+        <v>0.309</v>
+      </c>
+      <c r="AN10">
+        <v>-0.7359357060849598</v>
+      </c>
+      <c r="AO10">
+        <v>-5.11326860841424</v>
+      </c>
+      <c r="AP10">
+        <v>-0.7359357060849598</v>
+      </c>
+      <c r="AQ10">
+        <v>-5.11326860841424</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Goobit Group AB (publ) (NGM:BTCX)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>-0.01856287425149701</v>
+      </c>
+      <c r="H11">
+        <v>-0.09724550898203593</v>
+      </c>
+      <c r="I11">
+        <v>-0.1413173652694611</v>
+      </c>
+      <c r="J11">
+        <v>-0.1413173652694611</v>
+      </c>
+      <c r="K11">
+        <v>-1.71</v>
+      </c>
+      <c r="L11">
+        <v>-0.2047904191616766</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.404</v>
+      </c>
+      <c r="V11">
+        <v>0.1914691943127962</v>
+      </c>
+      <c r="W11">
+        <v>-0.7307692307692308</v>
+      </c>
+      <c r="X11">
+        <v>0.04981714963548235</v>
+      </c>
+      <c r="Y11">
+        <v>-0.7805863804047132</v>
+      </c>
+      <c r="Z11">
+        <v>5.968548963545389</v>
+      </c>
+      <c r="AA11">
+        <v>-0.8434596140100071</v>
+      </c>
+      <c r="AB11">
+        <v>0.04981714963548235</v>
+      </c>
+      <c r="AC11">
+        <v>-0.8932767636454895</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>-0.404</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.2368112543962486</v>
+      </c>
+      <c r="AK11">
+        <v>-1.315960912052118</v>
+      </c>
+      <c r="AL11">
+        <v>0.537</v>
+      </c>
+      <c r="AM11">
+        <v>0.537</v>
+      </c>
+      <c r="AN11">
+        <v>-0</v>
+      </c>
+      <c r="AO11">
+        <v>-2.197392923649907</v>
+      </c>
+      <c r="AP11">
+        <v>0.7799227799227799</v>
+      </c>
+      <c r="AQ11">
+        <v>-2.197392923649907</v>
       </c>
     </row>
   </sheetData>
